--- a/tools/importer/reports/import-nispera.report.xlsx
+++ b/tools/importer/reports/import-nispera.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-08-22T22:08:00.284Z</t>
+    <t>2026-08-24T16:23:12.077Z</t>
   </si>
   <si>
     <t>Contact Us | Fluence - A Siemens and AES Company</t>
@@ -91,7 +91,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-21T21:16:26.351Z</t>
+    <t>2026-08-24T16:22:59.345Z</t>
   </si>
   <si>
     <t>Fluence | A Siemens and AES Company</t>
@@ -112,7 +112,7 @@
     <t>mosaic</t>
   </si>
   <si>
-    <t>2026-08-22T23:54:16.170Z</t>
+    <t>2026-08-24T16:23:18.995Z</t>
   </si>
   <si>
     <t>Bidding Software for Wind, Solar, and Energy Storage</t>
@@ -133,7 +133,7 @@
     <t>nispera</t>
   </si>
   <si>
-    <t>2026-08-22T23:54:37.618Z</t>
+    <t>2026-08-24T16:23:27.372Z</t>
   </si>
   <si>
     <t>Asset Performance Management Software for Wind, Solar, Energy Storage</t>
